--- a/assets/Tableau de compétence - BTS SIO 2025.xlsx
+++ b/assets/Tableau de compétence - BTS SIO 2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raphaelharvent/Desktop/Cours AFPI/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raphaelharvent/Documents/GitHub/raphaelharvent.github.io/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8935F58-5214-EE42-969F-B21B754EDB2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99E6D64-F907-CB49-AD58-E5448E50EBD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="800" windowWidth="29400" windowHeight="17200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="50">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -120,11 +120,6 @@
 ▸Participer à l’évolution d’un site Web exploitant les données de l’organisation.</t>
   </si>
   <si>
-    <t xml:space="preserve">▸Analyser les objectifs et les modalités d’organisation d’un projet
-▸Plécartsanifier les activités
-▸Évaluer les indicateurs de suivi d’un projet et analyser les </t>
-  </si>
-  <si>
     <t>▸Réaliser les tests d’intégration et d’acceptation d’un service
 ▸Déployer un service
 ▸Accompagner les utilisateurs dans la mise en place d’un service</t>
@@ -141,9 +136,6 @@
   </si>
   <si>
     <t>Installation d'un serveur AD-DNS-DHCP</t>
-  </si>
-  <si>
-    <t>DATE</t>
   </si>
   <si>
     <t>X</t>
@@ -165,9 +157,6 @@
   </si>
   <si>
     <t>Spanning tree</t>
-  </si>
-  <si>
-    <t>Le modèle OSI</t>
   </si>
   <si>
     <t>Réalisations en milieu professionnel en cours de première année</t>
@@ -209,13 +198,21 @@
     <t>Signature et Tampon de l'entreprise</t>
   </si>
   <si>
-    <t>En cours</t>
+    <t>Decembre 2025 - Fevrier 2026</t>
   </si>
   <si>
-    <t>2025-2026</t>
+    <t xml:space="preserve"> Septembre 2024 - Juin 2025</t>
   </si>
   <si>
-    <t>2024-2026</t>
+    <t>Juin 2025 - Juin 2026</t>
+  </si>
+  <si>
+    <t>Octobre 2024 - Avril 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">▸Analyser les objectifs et les modalités d’organisation d’un projet
+▸Planifier les activités
+▸Évaluer les indicateurs de suivi d’un projet et analyser les </t>
   </si>
 </sst>
 </file>
@@ -762,7 +759,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -845,6 +842,39 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -886,38 +916,8 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="20" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1141,62 +1141,62 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="70.33203125" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="2" max="2" width="28.1640625" customWidth="1"/>
     <col min="3" max="8" width="18.6640625" customWidth="1"/>
     <col min="9" max="28" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="31" t="s">
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="32"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:13" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
     </row>
     <row r="3" spans="1:13" ht="23" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="39" t="s">
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="40"/>
-      <c r="H3" s="41"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="52"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="23" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="30"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="41"/>
       <c r="F4" s="2" t="s">
         <v>6</v>
       </c>
@@ -1208,22 +1208,22 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="23" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="38"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="49"/>
     </row>
     <row r="6" spans="1:13" ht="85" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="45" t="s">
+      <c r="A6" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="53" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -1246,8 +1246,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" ht="291.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="46"/>
-      <c r="B7" s="43"/>
+      <c r="A7" s="57"/>
+      <c r="B7" s="54"/>
       <c r="C7" s="7" t="s">
         <v>18</v>
       </c>
@@ -1258,295 +1258,298 @@
         <v>20</v>
       </c>
       <c r="F7" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="H7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="8" t="s">
+    </row>
+    <row r="8" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="55" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="44" t="s">
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="52"/>
+    </row>
+    <row r="9" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="41"/>
-    </row>
-    <row r="9" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="24" t="s">
+      <c r="B9" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="31"/>
+    </row>
+    <row r="10" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="50" t="s">
+      <c r="B10" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50" t="s">
-        <v>27</v>
+      <c r="B11" s="10" t="s">
+        <v>48</v>
       </c>
-      <c r="H9" s="52"/>
-    </row>
-    <row r="10" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="9" t="s">
+      <c r="C11" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="30"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="31"/>
+    </row>
+    <row r="12" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="25" t="s">
-        <v>26</v>
+      <c r="B12" s="10" t="s">
+        <v>48</v>
       </c>
-      <c r="C10" s="50" t="s">
-        <v>27</v>
+      <c r="C12" s="29"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="60" t="s">
+        <v>25</v>
       </c>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50" t="s">
-        <v>27</v>
+      <c r="F12" s="33"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="31" t="s">
+        <v>25</v>
       </c>
-      <c r="H10" s="52" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="9" t="s">
+    </row>
+    <row r="13" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="25" t="s">
-        <v>26</v>
+      <c r="B13" s="10" t="s">
+        <v>48</v>
       </c>
-      <c r="C11" s="50" t="s">
-        <v>27</v>
+      <c r="C13" s="30" t="s">
+        <v>25</v>
       </c>
-      <c r="D11" s="51"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="50" t="s">
-        <v>27</v>
+      <c r="D13" s="30"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="30" t="s">
+        <v>25</v>
       </c>
-      <c r="H11" s="52"/>
-    </row>
-    <row r="12" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="9" t="s">
+    </row>
+    <row r="14" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="25" t="s">
-        <v>26</v>
+      <c r="B14" s="10" t="s">
+        <v>48</v>
       </c>
-      <c r="C12" s="50"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="55" t="s">
-        <v>27</v>
+      <c r="C14" s="29" t="s">
+        <v>25</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="9" t="s">
+      <c r="D14" s="30"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="34"/>
+    </row>
+    <row r="15" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="25" t="s">
-        <v>26</v>
+      <c r="B15" s="10" t="s">
+        <v>48</v>
       </c>
-      <c r="C13" s="51" t="s">
-        <v>27</v>
+      <c r="C15" s="29" t="s">
+        <v>25</v>
       </c>
-      <c r="D13" s="51"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="51" t="s">
-        <v>27</v>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="30" t="s">
+        <v>25</v>
       </c>
-      <c r="H13" s="52"/>
-    </row>
-    <row r="14" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="51"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="56" t="s">
-        <v>27</v>
-      </c>
-      <c r="G14" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="H14" s="55"/>
-    </row>
-    <row r="15" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="H15" s="55"/>
+      <c r="H15" s="34"/>
     </row>
     <row r="16" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="50"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="55" t="s">
-        <v>27</v>
-      </c>
+      <c r="A16" s="9"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="34"/>
     </row>
     <row r="17" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="18" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="9"/>
       <c r="B18" s="25"/>
-      <c r="C18" s="50"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="55"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="34"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="34" t="s">
+      <c r="A19" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="46"/>
+    </row>
+    <row r="21" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" s="38"/>
+    </row>
+    <row r="22" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="38"/>
+    </row>
+    <row r="23" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="35"/>
-    </row>
-    <row r="21" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="24" t="s">
+      <c r="B23" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="H23" s="38"/>
+    </row>
+    <row r="24" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="25">
-        <v>2024</v>
+      <c r="B24" s="10" t="s">
+        <v>46</v>
       </c>
-      <c r="C21" s="49" t="s">
-        <v>27</v>
+      <c r="C24" s="36" t="s">
+        <v>25</v>
       </c>
-      <c r="D21" s="57"/>
-      <c r="E21" s="57"/>
-      <c r="F21" s="49"/>
-      <c r="G21" s="49"/>
-      <c r="H21" s="59"/>
-    </row>
-    <row r="22" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="26" t="s">
+      <c r="D24" s="28"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="G24" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="H24" s="38"/>
+    </row>
+    <row r="25" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="25">
-        <v>2024</v>
+      <c r="B25" s="10" t="s">
+        <v>46</v>
       </c>
-      <c r="C22" s="49"/>
-      <c r="D22" s="49" t="s">
-        <v>27</v>
+      <c r="C25" s="36" t="s">
+        <v>25</v>
       </c>
-      <c r="E22" s="57"/>
-      <c r="F22" s="57"/>
-      <c r="G22" s="57"/>
-      <c r="H22" s="59"/>
-    </row>
-    <row r="23" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="9" t="s">
+      <c r="D25" s="28"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" s="28"/>
+      <c r="H25" s="38"/>
+    </row>
+    <row r="26" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="25">
-        <v>2024</v>
+      <c r="B26" s="10" t="s">
+        <v>46</v>
       </c>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="49" t="s">
-        <v>27</v>
+      <c r="C26" s="28" t="s">
+        <v>25</v>
       </c>
-      <c r="H23" s="59" t="s">
-        <v>27</v>
+      <c r="D26" s="28"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="28" t="s">
+        <v>25</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="25">
-        <v>2024</v>
-      </c>
-      <c r="C24" s="57"/>
-      <c r="D24" s="49"/>
-      <c r="E24" s="57"/>
-      <c r="F24" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="G24" s="57"/>
-      <c r="H24" s="59"/>
-    </row>
-    <row r="25" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="25">
-        <v>2024</v>
-      </c>
-      <c r="C25" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" s="49"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
-      <c r="H25" s="59" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="25">
-        <v>2024</v>
-      </c>
-      <c r="C26" s="49" t="s">
-        <v>27</v>
-      </c>
-      <c r="D26" s="49"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="49" t="s">
-        <v>27</v>
-      </c>
-      <c r="G26" s="49"/>
-      <c r="H26" s="59"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="38"/>
     </row>
     <row r="27" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="25"/>
@@ -1558,84 +1561,88 @@
       <c r="H27" s="13"/>
     </row>
     <row r="28" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="34" t="s">
+      <c r="A28" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="40"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="46"/>
+    </row>
+    <row r="29" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="28"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G29" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="H29" s="37"/>
+    </row>
+    <row r="30" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" s="28"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="G30" s="28"/>
+      <c r="H30" s="37"/>
+    </row>
+    <row r="31" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="29"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="35"/>
-    </row>
-    <row r="29" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="24" t="s">
+      <c r="B31" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="36"/>
+      <c r="E31" s="36"/>
+      <c r="F31" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="G31" s="28"/>
+      <c r="H31" s="38"/>
+    </row>
+    <row r="32" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="27" t="s">
-        <v>48</v>
+      <c r="B32" s="27" t="s">
+        <v>47</v>
       </c>
-      <c r="C29" s="57" t="s">
-        <v>27</v>
+      <c r="C32" s="28"/>
+      <c r="D32" s="36" t="s">
+        <v>25</v>
       </c>
-      <c r="D29" s="49"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="49" t="s">
-        <v>27</v>
-      </c>
-      <c r="G29" s="49" t="s">
-        <v>27</v>
-      </c>
-      <c r="H29" s="58"/>
-    </row>
-    <row r="30" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B30" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="D30" s="49"/>
-      <c r="E30" s="57"/>
-      <c r="F30" s="57"/>
-      <c r="G30" s="49"/>
-      <c r="H30" s="58"/>
-    </row>
-    <row r="31" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B31" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="C31" s="49" t="s">
-        <v>27</v>
-      </c>
-      <c r="D31" s="57"/>
-      <c r="E31" s="57"/>
-      <c r="F31" s="57"/>
-      <c r="G31" s="49"/>
-      <c r="H31" s="59"/>
-    </row>
-    <row r="32" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B32" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="C32" s="49"/>
-      <c r="D32" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="E32" s="57"/>
-      <c r="F32" s="49"/>
-      <c r="G32" s="57"/>
-      <c r="H32" s="59"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="38"/>
     </row>
     <row r="33" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="9"/>
@@ -1679,7 +1686,7 @@
     </row>
     <row r="37" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="21" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B37" s="22"/>
       <c r="C37" s="23"/>
